--- a/schema_v2.xlsx
+++ b/schema_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2abd1f54496c410b/Documents/GCP_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_F25DC773A252ABDACC10481939DD4A0C5BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74367E3D-4D5A-4E9C-AFFE-DD5040DEF90D}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_F25DC773A252ABDACC10481939DD4A0C5BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF5609A-EE54-45EC-B67E-16E7EC32A06C}"/>
   <bookViews>
-    <workbookView xWindow="7760" yWindow="0" windowWidth="11530" windowHeight="12090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>accident_longitude</t>
   </si>
@@ -163,6 +163,10 @@
   <si>
     <t>A. sub_accident_history (歷史事故事件副表/fact)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>city</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -662,6 +666,9 @@
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D10" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">

--- a/schema_v2.xlsx
+++ b/schema_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2abd1f54496c410b/Documents/GCP_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_F25DC773A252ABDACC10481939DD4A0C5BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF5609A-EE54-45EC-B67E-16E7EC32A06C}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="11_F25DC773A252ABDACC10481939DD4A0C5BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7AB0681-77DD-4045-A8D7-54D56B852F13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
   <si>
     <t>accident_longitude</t>
   </si>
@@ -66,58 +66,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>B. weather_station（測站維度表 / dim）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>station_longitude</t>
-  </si>
-  <si>
-    <t>station_id (PK)</t>
-  </si>
-  <si>
-    <t>station_latitude</t>
-  </si>
-  <si>
-    <t>station_status</t>
-  </si>
-  <si>
-    <t>station_name</t>
-  </si>
-  <si>
     <t>C. weather_hourly（氣象小時觀測表 / fact）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>station_id</t>
-  </si>
-  <si>
-    <t>observation_hour</t>
-  </si>
-  <si>
-    <t>temperature</t>
-  </si>
-  <si>
-    <t>precipitation</t>
-  </si>
-  <si>
-    <t>date_opening</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>date_close</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>station_sea_level</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>…(詳細數據先略)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>…(詳細數據先略)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -166,6 +119,190 @@
   </si>
   <si>
     <t>city</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Station_record_id (PK)</t>
+  </si>
+  <si>
+    <t>Station_id (感覺索引可建立可不建，因為大約只有1000筆資料列)</t>
+  </si>
+  <si>
+    <t>Station_name</t>
+  </si>
+  <si>
+    <t>Station_sea_level</t>
+  </si>
+  <si>
+    <t>Station_latitude(WGS84)</t>
+  </si>
+  <si>
+    <t>Station_longitude(WGS84)</t>
+  </si>
+  <si>
+    <t>Station_working_State</t>
+  </si>
+  <si>
+    <t>State_valid_from</t>
+  </si>
+  <si>
+    <t>State_valid_to</t>
+  </si>
+  <si>
+    <t>Created_on</t>
+  </si>
+  <si>
+    <t>Updated_on</t>
+  </si>
+  <si>
+    <t>Created_by</t>
+  </si>
+  <si>
+    <t>Updated_by</t>
+  </si>
+  <si>
+    <t>station_record_id (FK)</t>
+  </si>
+  <si>
+    <t>Station_id (與Observation_datetime組成複合PK)</t>
+  </si>
+  <si>
+    <t>Observation_datetime (YYYY-MM-DD_HH:MM:SS)
+(與Station_id組成複合PK)</t>
+  </si>
+  <si>
+    <t>Station_air_pressure</t>
+  </si>
+  <si>
+    <t>Sea_pressure</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Temp_dew_point</t>
+  </si>
+  <si>
+    <t>Relative_humidity</t>
+  </si>
+  <si>
+    <t>Wind_speed</t>
+  </si>
+  <si>
+    <t>Wind_direction</t>
+  </si>
+  <si>
+    <t>Wind_speed_gust</t>
+  </si>
+  <si>
+    <t>Wind_distant_gust</t>
+  </si>
+  <si>
+    <t>Precipitation</t>
+  </si>
+  <si>
+    <t>Precipitation_hour</t>
+  </si>
+  <si>
+    <t>Sun_shine_hour</t>
+  </si>
+  <si>
+    <t>Global_radiation</t>
+  </si>
+  <si>
+    <t>Visibility</t>
+  </si>
+  <si>
+    <t>Visibility_mean_auto</t>
+  </si>
+  <si>
+    <t>UVI</t>
+  </si>
+  <si>
+    <t>Cloud_amount</t>
+  </si>
+  <si>
+    <t>Cloud_amount_by_satellites</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_0_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_5_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_10_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_20_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_30_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_50_cm</t>
+  </si>
+  <si>
+    <t>Soil_temp_at_100_cm</t>
+  </si>
+  <si>
+    <t>B. weather_station（測站 / fact）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>created_on</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>updated_on</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>created_by</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>updated_by</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>party_sq 1 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(30)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(15,4)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>str(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(200)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>datatime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -173,9 +310,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -234,25 +368,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -269,10 +391,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -538,208 +656,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53" style="4" customWidth="1"/>
-    <col min="2" max="2" width="45.59765625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.296875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="46.796875" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="4"/>
+    <col min="1" max="1" width="53" style="2" customWidth="1"/>
+    <col min="2" max="2" width="45.59765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="46.796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.8984375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="E6" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C30" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C31" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
